--- a/output/pdf_financials_xlsx/DS.xlsx
+++ b/output/pdf_financials_xlsx/DS.xlsx
@@ -2506,34 +2506,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>58.771934</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>8.367106</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.380947</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>9.729364</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.40449</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.130345</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>5.543744</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>7.152049</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.275175</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.557976</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.004993</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.222085999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2602,34 +2602,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>58.771934</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>8.367106</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.380947</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>9.729364</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.40449</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.130345</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>5.543744</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>7.152049</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.275175</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.557976</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.004993</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.222085999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3187,25 +3187,25 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>83.124066</v>
+        <v>73.394702</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>78.195457</v>
+        <v>72.79096699999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>80.938742</v>
+        <v>75.808397</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>80.502134</v>
+        <v>74.95838999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>79.389684</v>
+        <v>72.237635</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>73.25961100000001</v>
+        <v>68.984436</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>58.522002</v>
+        <v>54.964026</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">

--- a/output/pdf_financials_xlsx/DS.xlsx
+++ b/output/pdf_financials_xlsx/DS.xlsx
@@ -874,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.046282</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.044056</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.06321300000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.051408</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>0.020919</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.709349</v>
+        <v>0.7556310000000001</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1.350328</v>
@@ -22145,7 +22145,11 @@
           <t>Other operating costs</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -25739,7 +25743,11 @@
           <t>Other operating costs</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -27795,7 +27803,11 @@
           <t>Other operating costs</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
